--- a/solution_registry.xlsx
+++ b/solution_registry.xlsx
@@ -1,39 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\solution_registry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA3409BB-816A-4D3C-AA20-E8982BE2A69B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00615F3A-CFB7-4E36-9855-D82E17143A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="448">
   <si>
     <t>solution_name</t>
   </si>
@@ -47,1279 +34,1336 @@
     <t>solution_description</t>
   </si>
   <si>
-    <t>A.I. Prompt Generator</t>
-  </si>
-  <si>
     <t>AI_exploration_infrastructure</t>
   </si>
   <si>
+    <t>A sophisticated AI infrastructure that uses AI agents and LLMs to research an query population health data.</t>
+  </si>
+  <si>
     <t>Ai Agent</t>
   </si>
   <si>
+    <t>AI_Agent</t>
+  </si>
+  <si>
+    <t>Use uagent to Create AI agents to perform workflows and LLM integrations.</t>
+  </si>
+  <si>
     <t>Ai Chatbot</t>
   </si>
   <si>
+    <t>AI Chatbot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI chatbot using LLMS and RAG to ethically answer questions about private enterprise data </t>
+  </si>
+  <si>
+    <t>Ai Chatbot Architecture</t>
+  </si>
+  <si>
+    <t>ai_chatbot_architecture</t>
+  </si>
+  <si>
+    <t>Defines the technical architecture for AI Chatbot</t>
+  </si>
+  <si>
     <t>Ai Exploration Infrastructure Summary</t>
   </si>
   <si>
+    <t>AI_exploration_infrastructure_summary</t>
+  </si>
+  <si>
     <t>Ai Exploration Infrastructure Technical</t>
   </si>
   <si>
+    <t>AI_exploration_infrastructure_technical</t>
+  </si>
+  <si>
     <t>Ai Grading Plan Assistant</t>
   </si>
   <si>
+    <t>AI_Grading_Plan_Assistant</t>
+  </si>
+  <si>
+    <t>Utilizing an AI Assistant in innovative ways to enhance the civil engineering process of grading a property.</t>
+  </si>
+  <si>
     <t>Ai Grading Plans</t>
   </si>
   <si>
+    <t>AI Grading Plans</t>
+  </si>
+  <si>
+    <t>Utilizing AI in innovative ways to enhance the civil engineering process of grading a property.</t>
+  </si>
+  <si>
     <t>Ai Test Framework</t>
   </si>
   <si>
+    <t>AI_test_framework</t>
+  </si>
+  <si>
+    <t>Establishes infrastructure for testing AI platform.</t>
+  </si>
+  <si>
     <t>Archival Automation</t>
   </si>
   <si>
+    <t>archival_automation</t>
+  </si>
+  <si>
+    <t>Archival Automation automatically backs up your data and puts a archive  stamp on it.</t>
+  </si>
+  <si>
     <t>Authentication</t>
   </si>
   <si>
+    <t>User and password authentication</t>
+  </si>
+  <si>
     <t>Autogen</t>
   </si>
   <si>
+    <t>autogen</t>
+  </si>
+  <si>
+    <t>Use autogen AI agents to perform workflows and LLM integrations.</t>
+  </si>
+  <si>
     <t>Automated Application Launcher</t>
   </si>
   <si>
+    <t>automated_application_launcher</t>
+  </si>
+  <si>
+    <t>Automated Application Launcher launches any application you want on a schedule or through voice commands</t>
+  </si>
+  <si>
+    <t>Avatar Creation</t>
+  </si>
+  <si>
+    <t>avatar_creation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning how to trade GOLD futures </t>
+  </si>
+  <si>
+    <t>Bridgeinspection</t>
+  </si>
+  <si>
+    <t>bridgeinspection</t>
+  </si>
+  <si>
+    <t>Exploratory AI tools for Civil Engineering for Bridge Inspection</t>
+  </si>
+  <si>
     <t>Calculator</t>
   </si>
   <si>
+    <t>calculator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build a simple calculator using python and tkinter to enhance your programming skills </t>
+  </si>
+  <si>
     <t>Cancer Care Timeline</t>
   </si>
   <si>
+    <t>cancer_care_timeline</t>
+  </si>
+  <si>
+    <t>Analyzing each patients temporal pathway through their cancer treatment and survivorship.</t>
+  </si>
+  <si>
     <t>Cancer Treatment Outcomes</t>
   </si>
   <si>
+    <t>cancer_treatment_outcomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provides a list of measurable outcomes for Cancer Care including remission, ongoing treatment, active surveillance, death, etc.  </t>
+  </si>
+  <si>
     <t>Cancer Treatment Side Effects</t>
   </si>
   <si>
+    <t>cancer_treatment_side_effects</t>
+  </si>
+  <si>
+    <t>quantifying of side affects associated with major cancer treatment modalities</t>
+  </si>
+  <si>
     <t>Chat Gpt Integration</t>
   </si>
   <si>
+    <t>chat_gpt_integration</t>
+  </si>
+  <si>
+    <t>Solution that demonstrates how to integrate your applications with **Chat GPT**. Utilizes the API to integrate with the LLM **Large Language Model**</t>
+  </si>
+  <si>
     <t xml:space="preserve">Choropleth Map </t>
   </si>
   <si>
+    <t>choropleth_map</t>
+  </si>
+  <si>
+    <t>Mapping solution for global and local choropleth maps</t>
+  </si>
+  <si>
+    <t>Provide a set of images designed to brand and represent each unique solution.</t>
+  </si>
+  <si>
     <t>Chronic Disease Registry</t>
   </si>
   <si>
+    <t>chronic_disease_registry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A chronic disease registry classifies patients with specific diseases or conditions. </t>
+  </si>
+  <si>
     <t>Clinical Classification System</t>
   </si>
   <si>
-    <t>Common Skiing Injuries</t>
+    <t>clinical_classification_system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This solution extends and enhances the ICD-10-CM diagnosis standard to include disease classifications that can be used for registries and care outreach. </t>
+  </si>
+  <si>
+    <t>Community Engagement Plan</t>
+  </si>
+  <si>
+    <t>community_engagement_plan</t>
+  </si>
+  <si>
+    <t>Defines the approach and validation plan for engageing the community in an AI chatbot assistant</t>
   </si>
   <si>
     <t>Configuring Settings</t>
   </si>
   <si>
+    <t>configuring_settings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solution for Configuring Settings. The config.ini file in Python serves as a centralized repository for storing configuration parameters, </t>
+  </si>
+  <si>
     <t>Convert MS Access to New Technology</t>
   </si>
   <si>
+    <t>convert_msaccess</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solution for converting MS access into a new technology stack. </t>
+  </si>
+  <si>
     <t>Corpus</t>
   </si>
   <si>
+    <t>corpus</t>
+  </si>
+  <si>
     <t>Correlation Heatmap</t>
   </si>
   <si>
+    <t>correlation_heatmap</t>
+  </si>
+  <si>
+    <t>A correlation heatmap provides insights to critical relationships within Data</t>
+  </si>
+  <si>
     <t>Create Readme Md</t>
   </si>
   <si>
+    <t>create_readme_md</t>
+  </si>
+  <si>
+    <t>Generate a beautiful and effective readme.md file.</t>
+  </si>
+  <si>
     <t>Create Sign</t>
   </si>
   <si>
+    <t>create_sign</t>
+  </si>
+  <si>
+    <t>A tiny utility to create PNG signs.</t>
+  </si>
+  <si>
     <t>Create Solution Definition</t>
   </si>
   <si>
+    <t>create_solution_definition</t>
+  </si>
+  <si>
+    <t>A utility to create a new definition  for every solution.</t>
+  </si>
+  <si>
     <t>Create Solution Sign</t>
   </si>
   <si>
+    <t>create_solution_sign</t>
+  </si>
+  <si>
+    <t>A utility to create a new PNG sign for every solution.</t>
+  </si>
+  <si>
     <t>Create Solution Word Cloud</t>
   </si>
   <si>
+    <t>create_solution_word_cloud</t>
+  </si>
+  <si>
+    <t>A utility to create a word cloud for every solution.</t>
+  </si>
+  <si>
     <t>Curated Datasets</t>
   </si>
   <si>
+    <t>curated_datasets</t>
+  </si>
+  <si>
+    <t>Solution for Curated Datasets</t>
+  </si>
+  <si>
     <t xml:space="preserve">Daily Data Loader  </t>
   </si>
   <si>
+    <t>daily_data_loader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load a the LATEST DELTA of NEW TRANSACTIONS  into a relational datastore. Run periodically for freshness. </t>
+  </si>
+  <si>
     <t>Data Analysis Story Board</t>
   </si>
   <si>
+    <t>data_analysis_story_board</t>
+  </si>
+  <si>
+    <t>A story board document of data amalysis from start to finish.</t>
+  </si>
+  <si>
     <t>Data Cleansing</t>
   </si>
   <si>
+    <t>data_cleansing</t>
+  </si>
+  <si>
+    <t>A set of utilities to easily cleans and improve your data</t>
+  </si>
+  <si>
     <t>Data Delta Calculator</t>
   </si>
   <si>
+    <t>data_delta_calculator</t>
+  </si>
+  <si>
+    <t>Calculates the structural difference between raw data sources. Compares to LAST LOAD to determine what is NEW. This is for loading data incrementally over time so that history isn't constantly re-loaded</t>
+  </si>
+  <si>
     <t>Data Discovery</t>
   </si>
   <si>
+    <t>data_discovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finds ALL the valuable data assets on your system and registers them. </t>
+  </si>
+  <si>
     <t xml:space="preserve">Data Loader Reference Tables </t>
   </si>
   <si>
+    <t>data_loader_reference_tables</t>
+  </si>
+  <si>
+    <t>Load a series of reference tables into a relational datastore</t>
+  </si>
+  <si>
     <t xml:space="preserve">Data Loader Transactional  Tables </t>
   </si>
   <si>
+    <t>data_loader_transactional__tables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load a large historical transactional tables into a relational datastore. One Time LOAD </t>
+  </si>
+  <si>
     <t>Data Profiling</t>
   </si>
   <si>
+    <t>data_profiling</t>
+  </si>
+  <si>
+    <t>Tells you **EVERYTHING** about your data.</t>
+  </si>
+  <si>
+    <t>Tells you **EVERYTHING** about your data…  **easily** discover any issues in your data</t>
+  </si>
+  <si>
     <t>Data Science Report Generator</t>
   </si>
   <si>
+    <t>data_science_report_generator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This project creates a word document for data science projects that produces a report of the scientific </t>
+  </si>
+  <si>
     <t>Data Sets</t>
   </si>
   <si>
+    <t>data_sets</t>
+  </si>
+  <si>
+    <t>A repository of curated datasets for data science projects</t>
+  </si>
+  <si>
     <t>Db Analysis</t>
   </si>
   <si>
+    <t>DB_Analysis</t>
+  </si>
+  <si>
+    <t>Perform database analysis on ANY database to generate the schema and Data Discription Language.</t>
+  </si>
+  <si>
     <t>Db Discovery</t>
   </si>
   <si>
+    <t>DB_Discovery</t>
+  </si>
+  <si>
+    <t>Perform database discovery on ANY database to generate the Schema and Data Discription Language.</t>
+  </si>
+  <si>
     <t>Descriptive Statistics</t>
   </si>
   <si>
+    <t>descriptive_statistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">process used to analyze the data. </t>
+  </si>
+  <si>
+    <t>Descriptive statistics summarize and describe the main features of a dataset through measures such as mean, median, mode, standard deviation, and visualizations.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Design Goals </t>
   </si>
   <si>
+    <t>design_goal</t>
+  </si>
+  <si>
     <t>Diabetes Outcome Analysis</t>
   </si>
   <si>
+    <t>diabetes_outcome_analysis</t>
+  </si>
+  <si>
+    <t>A analysis of outcomes related to diabetes treatments</t>
+  </si>
+  <si>
     <t>Diabetes Risk Stratification.</t>
   </si>
   <si>
+    <t>diabetes_risk_stratification</t>
+  </si>
+  <si>
+    <t>Machine Learning Risk stratification - 3 different approaches</t>
+  </si>
+  <si>
     <t>Disease Progression Model</t>
   </si>
   <si>
+    <t>disease_progression_model</t>
+  </si>
+  <si>
+    <t>Solution for Disease Progression Model</t>
+  </si>
+  <si>
     <t>Docling</t>
   </si>
   <si>
+    <t>docling</t>
+  </si>
+  <si>
+    <t>Utilize docling to build a knowledge base out of ANY document so an AI LLM query the data</t>
+  </si>
+  <si>
     <t>Domain Topic Classifier</t>
   </si>
   <si>
+    <t>domain_topic_classifier</t>
+  </si>
+  <si>
+    <t>identify the most likely knowledge domain and topic based upon keywords</t>
+  </si>
+  <si>
     <t>Email Automation</t>
   </si>
   <si>
+    <t>email_automation</t>
+  </si>
+  <si>
+    <t>Solution for Email Automation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Environment Testing </t>
   </si>
   <si>
+    <t>environment_testing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Makes sure all your computing resources are ready to perform complex workflows. </t>
+  </si>
+  <si>
     <t>Epidemiology Methodology</t>
   </si>
   <si>
+    <t>epidemiology_methodology</t>
+  </si>
+  <si>
+    <t>The epidemiology methodology establishes a versatile data science methodology for epidemiology projects spanning various conditions or diseases The approach begins with comprehensive data collection, encompassing demographics, environmental factors, and relevant health metrics. Employing advanced statistical analyses and machine learning algorithms, the methodology aims to discern patterns, identify risk factors, and optimize predictive models, fostering a holistic understanding of the factors influencing the studied health outcomes.</t>
+  </si>
+  <si>
     <t>File Discovery</t>
   </si>
   <si>
+    <t>file_discovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discovers where your critical data is and provides archives. </t>
+  </si>
+  <si>
     <t>File Manager</t>
   </si>
   <si>
+    <t>file_manager</t>
+  </si>
+  <si>
+    <t>Solution for File Manager</t>
+  </si>
+  <si>
     <t>File Removal</t>
   </si>
   <si>
+    <t>file_removal</t>
+  </si>
+  <si>
+    <t>Solution for File Removal</t>
+  </si>
+  <si>
     <t>File Watchdog</t>
   </si>
   <si>
+    <t>file_watchdog</t>
+  </si>
+  <si>
+    <t>Solution for File Watchdog</t>
+  </si>
+  <si>
     <t>Form Validator</t>
   </si>
   <si>
+    <t>form_validator</t>
+  </si>
+  <si>
+    <t>Solution for Form Validator</t>
+  </si>
+  <si>
+    <t>Gemini Tools</t>
+  </si>
+  <si>
+    <t>Gemini_Tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seven new google gemini AI tools </t>
+  </si>
+  <si>
     <t>Getting Started with Django</t>
   </si>
   <si>
+    <t>getting_started_with_django</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git allows you to quickly download pre-built solutions  </t>
+  </si>
+  <si>
     <t>Git Commands</t>
   </si>
   <si>
+    <t>git_commands</t>
+  </si>
+  <si>
     <t>Github Automation</t>
   </si>
   <si>
+    <t>github_automation</t>
+  </si>
+  <si>
+    <t>Git is a distributed version control system designed to track changes in source code during software development.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Glossary Term </t>
   </si>
   <si>
+    <t>glossary_term</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glossary of terms </t>
+  </si>
+  <si>
     <t>HTML_to_Document</t>
   </si>
   <si>
+    <t>A utility to create a word document docx out of HTML documents.</t>
+  </si>
+  <si>
     <t>Happiness Datasets</t>
   </si>
   <si>
+    <t>happiness_datasets</t>
+  </si>
+  <si>
+    <t>A repository  for Happiness Datasets</t>
+  </si>
+  <si>
+    <t>Healtheintellegence</t>
+  </si>
+  <si>
+    <t>healtheintellegence</t>
+  </si>
+  <si>
+    <t>Exploratory Health care assistent using latest AI Tools</t>
+  </si>
+  <si>
     <t>High Risk High Need</t>
   </si>
   <si>
+    <t>high_risk_high_need</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automates triage of high risk - high need patients </t>
+  </si>
+  <si>
     <t>Hole In One</t>
   </si>
   <si>
+    <t>hole_in_one</t>
+  </si>
+  <si>
+    <t>A proven holistic approach to a better life with greater happiness.</t>
+  </si>
+  <si>
     <t>Html To Document</t>
   </si>
   <si>
+    <t>HTML_to_document</t>
+  </si>
+  <si>
     <t>Hugging Face Transformers</t>
   </si>
   <si>
+    <t>hugging_face_transformers</t>
+  </si>
+  <si>
+    <t>Solution for Hugging Face Transformers</t>
+  </si>
+  <si>
     <t>Incremental Imports</t>
   </si>
   <si>
+    <t>incremental_imports</t>
+  </si>
+  <si>
+    <t>Solution for Incremental Imports</t>
+  </si>
+  <si>
     <t>Infrastructure Setup</t>
   </si>
   <si>
+    <t>infrastructure_setup</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> This solution establishes an Infrastructure Directory to copy, secure. maintain, and archive All of your work in progress.  </t>
+  </si>
+  <si>
     <t xml:space="preserve">Intelligent Chatbot Corpus Learning </t>
   </si>
   <si>
+    <t>intelligent_chatbot_corpus_learning</t>
+  </si>
+  <si>
+    <t>[5]:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chatbot instantly scrapes reads any corpus or dataset. Learns it and provides a conversation about it. </t>
+  </si>
+  <si>
     <t xml:space="preserve">Intelligent Chatbot Data Serialization </t>
   </si>
   <si>
+    <t>intelligent_chatbot_data_serialization</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># Calculate and classify the process performance </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chatbot instantly scrapes reads any relational datastore, excel spreadsheet and segmentizes it. Uses NLP to for paragraphs and answer in natural language.  </t>
+  </si>
+  <si>
     <t xml:space="preserve">Intelligent Chatbot Generative Digital Assistant </t>
   </si>
   <si>
+    <t>intelligent_chatbot_generative_digital_assistant</t>
+  </si>
+  <si>
+    <t>status = ql.calculate_process_performance(solution_name, start_time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chatbot Assistant performs almost ANY task you can think of. This is your custom "Alexa" it opens mail, formats excel sheets, reads to you, tells jokes, and writes a swimming program for you.  Embedded ChatGPT 4. </t>
+  </si>
+  <si>
     <t xml:space="preserve">Intelligent Chatbot Web Scrapping  </t>
   </si>
   <si>
+    <t>intelligent_chatbot_web_scrapping</t>
+  </si>
+  <si>
+    <t>print(ql.append_log_file(solution_name))</t>
+  </si>
+  <si>
+    <t>Chatbot instantly scrapes your or anyone else's website. Learns it and provides a conversation about it. Use this to digitally engage your clients.</t>
+  </si>
+  <si>
     <t>Introduction To Pandas</t>
   </si>
   <si>
+    <t>introduction_to_pandas</t>
+  </si>
+  <si>
+    <t>Pandas is a powerful Python library used for data manipulation and analysis.</t>
+  </si>
+  <si>
     <t>Kids Abc Book</t>
   </si>
   <si>
+    <t>kids_abc_book</t>
+  </si>
+  <si>
+    <t>2024-03-15 10:39:07,381 - INFO - START solution_temple Start Time = 2024-03-15 10:39:07</t>
+  </si>
+  <si>
+    <t>Solution for Kids ABC Book</t>
+  </si>
+  <si>
     <t>Knowledge Transfer Solution</t>
   </si>
   <si>
+    <t>Knowledge_Transfer_Solution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Knowledge Transfer for AI Solutions - Transfering REPOS. </t>
+  </si>
+  <si>
     <t>Langgraph</t>
   </si>
   <si>
+    <t>LangGraph</t>
+  </si>
+  <si>
+    <t>Orchestrate Agentic AI with LangGraph and LangChain</t>
+  </si>
+  <si>
     <t>Library Installer</t>
   </si>
   <si>
+    <t>library_installer</t>
+  </si>
+  <si>
+    <t>2024-03-15 10:39:07,381 - INFO - solution_temple Step 0 - Initialize the configuration file parser</t>
+  </si>
+  <si>
+    <t>Solution for Library Installer</t>
+  </si>
+  <si>
     <t>Library for Logging And Debugging</t>
   </si>
   <si>
+    <t>quick_logger</t>
+  </si>
+  <si>
+    <t>2024-03-15 10:39:07,382 - INFO - Process solution_temple Step 0 - Initializing and starting Logging Process.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.py library for easily using logging and debugging. </t>
+  </si>
+  <si>
     <t>Logging And Debugging</t>
   </si>
   <si>
+    <t>logging_and_debugging</t>
+  </si>
+  <si>
+    <t>2024-03-15 10:39:07,391 - INFO - PERFORMANCE solution_temple The total process duration was:0.01</t>
+  </si>
+  <si>
+    <t>Solution for Logging And Debugging</t>
+  </si>
+  <si>
     <t>Magic Classifier</t>
   </si>
   <si>
+    <t>magic_classifier</t>
+  </si>
+  <si>
+    <t>identify if a magic command is found if chat input based upon magic keywords</t>
+  </si>
+  <si>
     <t>Managing Personas</t>
   </si>
   <si>
+    <t>managing_personas</t>
+  </si>
+  <si>
+    <t>2024-03-15 10:39:07,391 - INFO - PERFORMANCE solution_temple Stop Time = 2024-03-15 10:39:07</t>
+  </si>
+  <si>
+    <t>Generate and manage personas of any type to Make Chat GPT even MORE AMAZING !!!!</t>
+  </si>
+  <si>
     <t>Mark Down To Html</t>
   </si>
   <si>
+    <t>mark_down_to_HTML</t>
+  </si>
+  <si>
+    <t>A utility to create a web page HTML out of mark down documents.</t>
+  </si>
+  <si>
     <t>Membership Matching</t>
   </si>
   <si>
+    <t>membership_matching</t>
+  </si>
+  <si>
+    <t>2024-03-15 10:39:07,391 - INFO - PERFORMANCE solution_temple Short process duration less than 3 Seconds:0.01</t>
+  </si>
+  <si>
+    <t>Solution for Membership Matching</t>
+  </si>
+  <si>
     <t>Microsoft Azure</t>
   </si>
   <si>
+    <t>microsoft_azure</t>
+  </si>
+  <si>
+    <t>A learning pathway for microsoft azure AI fundamentals.</t>
+  </si>
+  <si>
     <t>Midastouch</t>
   </si>
   <si>
+    <t>MidasTouch</t>
+  </si>
+  <si>
     <t>Multi Disciplinary Cancer Care Team</t>
   </si>
   <si>
+    <t>multi_disciplinary_cancer_care_team</t>
+  </si>
+  <si>
+    <t>2024-03-15 10:39:07,391 - INFO - PERFORMANCE solution_temple Performance optimization is not reccomended</t>
+  </si>
+  <si>
+    <t>Identify the multidisciplinary cancer care team roles and responsibilities in cancer treatment.</t>
+  </si>
+  <si>
     <t>Nlp To Sql Training Data Builder</t>
   </si>
   <si>
+    <t>nlp_to_sql_training_data_builder</t>
+  </si>
+  <si>
+    <t>establishes training data for AI chatbot</t>
+  </si>
+  <si>
     <t>Notebook Clone</t>
   </si>
   <si>
+    <t>notebook_clone</t>
+  </si>
+  <si>
+    <t>2024-03-15 10:39:07,391 - INFO - END solution_temple =============================================</t>
+  </si>
+  <si>
+    <t>Solution for Notebook Clone</t>
+  </si>
+  <si>
     <t>Oncology Procedures Classification</t>
   </si>
   <si>
+    <t>oncology_procedures_classification</t>
+  </si>
+  <si>
+    <t>Process for classifying oncology procedures.</t>
+  </si>
+  <si>
     <t>Oncology Terminology</t>
   </si>
   <si>
+    <t>oncology_terminology</t>
+  </si>
+  <si>
+    <t>A dictionary of oncology  terminology.</t>
+  </si>
+  <si>
     <t>Patient Cancer Risk Index</t>
   </si>
   <si>
+    <t>patient_cancer_risk_index</t>
+  </si>
+  <si>
+    <t>Analyzing each patients risk for developing cancer within next year.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Patient Complexity Index </t>
   </si>
   <si>
+    <t>patient_complexity_index</t>
+  </si>
+  <si>
+    <t>Click to add a cell.</t>
+  </si>
+  <si>
+    <t>Solution for calculating a patients complexity based upon their diagnostic profile.</t>
+  </si>
+  <si>
     <t>Patient Word Cloud</t>
   </si>
   <si>
+    <t>patient_word_cloud</t>
+  </si>
+  <si>
+    <t>Solution for Patient Word Cloud</t>
+  </si>
+  <si>
     <t>Penguins</t>
   </si>
   <si>
+    <t>penguins</t>
+  </si>
+  <si>
+    <t>Solution for Penguins</t>
+  </si>
+  <si>
     <t xml:space="preserve">Poor Emotional Regulatory Control </t>
   </si>
   <si>
+    <t>poor_emotional_regulatory_control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculation and stratification of Risk based upon survey (BRFSS) of specific control behaviors (eating disorders, binge dirking, or substance abuse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculation and stratification of Risk based upon survey (BRFSS) of specific control behaviors (eating disorders, binge drinking, or substance abuse </t>
+  </si>
+  <si>
+    <t>Population Health Validation Plan</t>
+  </si>
+  <si>
+    <t>population_health_validation_plan</t>
+  </si>
+  <si>
+    <t>Defines the epidemological approach for validating population health data sets</t>
+  </si>
+  <si>
     <t>Precision Oncology</t>
   </si>
   <si>
+    <t>precision_oncology</t>
+  </si>
+  <si>
+    <t>Analysis of needs for current state of precision oncology.</t>
+  </si>
+  <si>
     <t>Predicting Breast Cancer</t>
   </si>
   <si>
+    <t>predicting_breast_cancer</t>
+  </si>
+  <si>
+    <t>Machine learning for predicting breast cancer.</t>
+  </si>
+  <si>
     <t>Predicting Colorectal Cancer</t>
   </si>
   <si>
+    <t>predicting_colorectal_cancer</t>
+  </si>
+  <si>
+    <t>Machine learning for predicting colorectal cancer.</t>
+  </si>
+  <si>
     <t>Predicting Diabetes</t>
   </si>
   <si>
+    <t>predicting_diabetes</t>
+  </si>
+  <si>
+    <t>Machine learning for predicting diabetes.</t>
+  </si>
+  <si>
     <t>Predicting Lung Cancer</t>
   </si>
   <si>
+    <t>predicting_lung_cancer</t>
+  </si>
+  <si>
+    <t>Machine learning for predicting lung cancer.</t>
+  </si>
+  <si>
     <t>Principal Component Analysis</t>
   </si>
   <si>
+    <t>principal_component_analysis</t>
+  </si>
+  <si>
+    <t>Solution for Principal Component Analysis</t>
+  </si>
+  <si>
     <t>Producing The Voice Over</t>
   </si>
   <si>
+    <t>producing_the_voice_over</t>
+  </si>
+  <si>
+    <t>Converts solution documentation to MP3 audio for voice over</t>
+  </si>
+  <si>
     <t>Progress Bar</t>
   </si>
   <si>
+    <t>progress_bar</t>
+  </si>
+  <si>
+    <t>Solution for Progress Bar</t>
+  </si>
+  <si>
     <t>Python Foundation</t>
   </si>
   <si>
+    <t>python_foundation</t>
+  </si>
+  <si>
+    <t>Solution for Python Foundation</t>
+  </si>
+  <si>
     <t>Registering Library To Pypi</t>
   </si>
   <si>
+    <t>registering_library_to_pypi</t>
+  </si>
+  <si>
+    <t>Register your python libraries to pypi to make them pip and uv installable</t>
+  </si>
+  <si>
     <t>Remote Process Automation Excel</t>
   </si>
   <si>
+    <t>remote_process_automation_excel</t>
+  </si>
+  <si>
+    <t>Makes excel files pretty, more functional , and easier to use.  This one solution saves hours !!!!</t>
+  </si>
+  <si>
     <t>Research Canvas</t>
   </si>
   <si>
+    <t>research_canvas</t>
+  </si>
+  <si>
+    <t>Utilizing an AI Assistant to create re usable research workflows and pathways. research canvas to collaborate and share work</t>
+  </si>
+  <si>
     <t>Rules Engine</t>
   </si>
   <si>
+    <t>rules_engine</t>
+  </si>
+  <si>
+    <t>Automated rules engine for dynamically analyzing data quality.</t>
+  </si>
+  <si>
     <t>SQLite Introduction</t>
   </si>
   <si>
+    <t>sqlite_introduction</t>
+  </si>
+  <si>
+    <t>SQLite introduction provides an introduction to SQL lite</t>
+  </si>
+  <si>
+    <t>sqlite_introduction provides an introduction to SQL lite</t>
+  </si>
+  <si>
     <t>Simple Chatbot Simple Nlp Response</t>
   </si>
   <si>
+    <t>simple_chatbot_simple_nlp_response</t>
+  </si>
+  <si>
+    <t>OLD SCHOOL Chatbot- Like LEXI of olden days with pre-built response lexicon …. But with advanced natural language built in.</t>
+  </si>
+  <si>
     <t>Smart Mini Proposal</t>
   </si>
   <si>
+    <t>smart_mini_proposal</t>
+  </si>
+  <si>
+    <t>Creates a mini proposal using a template and SMART criteria.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Solution Registry </t>
   </si>
   <si>
+    <t>solution_registry</t>
+  </si>
+  <si>
+    <t>Solution Registry - houses a list of solutions</t>
+  </si>
+  <si>
     <t>Streamlit</t>
   </si>
   <si>
+    <t xml:space="preserve">Streamlit UI for analytics catalogue </t>
+  </si>
+  <si>
     <t xml:space="preserve">Supervised Learning </t>
   </si>
   <si>
+    <t>supervised_learning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A very tiny example of supervised learning. </t>
+  </si>
+  <si>
+    <t>Provides general system information including CURRENT  memory / CPU usage</t>
+  </si>
+  <si>
     <t>System Information</t>
   </si>
   <si>
+    <t>system_information</t>
+  </si>
+  <si>
     <t>Talking Code</t>
   </si>
   <si>
+    <t>talking_code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application for building sophisticated text to speech </t>
+  </si>
+  <si>
     <t>Task Scheduling</t>
   </si>
   <si>
+    <t>task_scheduling</t>
+  </si>
+  <si>
+    <t>Schedules tasks and executes runtimes</t>
+  </si>
+  <si>
     <t>Thriveai</t>
   </si>
   <si>
+    <t>ThriveAI</t>
+  </si>
+  <si>
+    <t>Empowering organizations to harness the transformative potential of artificial intelligence</t>
+  </si>
+  <si>
+    <t>Thriveaistrategy</t>
+  </si>
+  <si>
+    <t>thriveaistrategy</t>
+  </si>
+  <si>
+    <t>Strategies for Thrive AI expansion</t>
+  </si>
+  <si>
     <t>Unzip Automation</t>
   </si>
   <si>
+    <t>unzip_automation</t>
+  </si>
+  <si>
+    <t>Solution for Unzip Automation</t>
+  </si>
+  <si>
     <t>Update Solution Images</t>
   </si>
   <si>
+    <t>update_solution_images</t>
+  </si>
+  <si>
     <t>Updating Libraries</t>
   </si>
   <si>
+    <t>updating_libraries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Makes sure the LATEST technology is used. </t>
+  </si>
+  <si>
     <t>Web Automation</t>
   </si>
   <si>
+    <t>web_automation</t>
+  </si>
+  <si>
+    <t>Solution for Web Automation</t>
+  </si>
+  <si>
+    <t>Welltellai</t>
+  </si>
+  <si>
+    <t>welltellai</t>
+  </si>
+  <si>
     <t>Word Cloud</t>
   </si>
   <si>
+    <t>word_cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produces a word cloud using the3 most relevant terminology using whatever cloud shape is supplied. </t>
+  </si>
+  <si>
     <t>World Mood</t>
   </si>
   <si>
+    <t>world_mood</t>
+  </si>
+  <si>
+    <t>Solution for World Mood</t>
+  </si>
+  <si>
     <t>ai_chatbot_scorecard</t>
   </si>
   <si>
+    <t>AI_chatbot_scorecard</t>
+  </si>
+  <si>
+    <t>The 7 Layer System Response Score is a comprehensive, domain specific evaluation framework that rates chatbot responses from 0 to 100.</t>
+  </si>
+  <si>
+    <t>The 7 Layer System Response Score is a comprehensive, domain specific evaluation framework that rates chatbot responses from 0 to 100.</t>
+  </si>
+  <si>
     <t>automating_windows_task_scheduler</t>
   </si>
   <si>
+    <t>This solution automates creating python script to run in windows task scheduler.</t>
+  </si>
+  <si>
     <t>corpus_learning_chatbot</t>
   </si>
   <si>
+    <t>chatbot that uses Natural language processing NLP to  learn from a specified corpus</t>
+  </si>
+  <si>
     <t>create_solution</t>
   </si>
   <si>
-    <t>data_analysis_story_board</t>
+    <t xml:space="preserve">Template for kick starting sophisticated python projects </t>
+  </si>
+  <si>
+    <t>A story board document of data analysis from start to finish.</t>
   </si>
   <si>
     <t>data_editor</t>
   </si>
   <si>
+    <t>Streamlit app for editing and persisting changes to data</t>
+  </si>
+  <si>
     <t>diagrams</t>
   </si>
   <si>
+    <t>A repository for diagrams</t>
+  </si>
+  <si>
     <t>ethical_guardrails</t>
   </si>
   <si>
+    <t>This solution includes a set of Ethical Guardrails designed to detect and prevent inappropriate, biased, or harmful outputs from AI systems.</t>
+  </si>
+  <si>
     <t>generate_sql</t>
   </si>
   <si>
+    <t>Generates SQL templates for Datasets</t>
+  </si>
+  <si>
     <t>icd_10_cm_analysis</t>
   </si>
   <si>
+    <t xml:space="preserve">Analyze the Internation Classification of Disease ICD-10-CM </t>
+  </si>
+  <si>
     <t>inventory_your_python</t>
   </si>
   <si>
-    <t>mark_down_to_HTML</t>
-  </si>
-  <si>
-    <t>multi_disciplinary_cancer_care_team</t>
-  </si>
-  <si>
     <t>oncology_diagnostic_coding</t>
   </si>
   <si>
+    <t>Define and classify diagnosis for all forms of cancer.</t>
+  </si>
+  <si>
     <t>oncology_epidemiology</t>
   </si>
   <si>
-    <t>patient_cancer_risk_index</t>
+    <t xml:space="preserve">Epidemiology methodology for oncology </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solution for calculating  patients lieklihood to develop cancer within the next year. </t>
   </si>
   <si>
     <t>patient_gaps_in_care</t>
   </si>
   <si>
+    <t>A report on specific patients gaps in care</t>
+  </si>
+  <si>
     <t>quality_of_life_index</t>
   </si>
   <si>
+    <t>Calculated index of monthly life quality from initial (denovo) diagnosis of major disease</t>
+  </si>
+  <si>
     <t>streamlit</t>
   </si>
   <si>
     <t>taipy_web_gui</t>
   </si>
   <si>
+    <t>Machine learning with Taipy web GUI and tensorflow ML</t>
+  </si>
+  <si>
     <t>term_frequency_inverse_document_frequency</t>
   </si>
   <si>
+    <t>TF-IDF helps identify important terms within a document by giving higher weights to terms that are frequent in the document but rare in the corpus</t>
+  </si>
+  <si>
     <t>titanic_survival_analysis</t>
-  </si>
-  <si>
-    <t>ai_prompt_generator</t>
-  </si>
-  <si>
-    <t>AI_Agent</t>
-  </si>
-  <si>
-    <t>AI Chatbot</t>
-  </si>
-  <si>
-    <t>AI_exploration_infrastructure_summary</t>
-  </si>
-  <si>
-    <t>AI_exploration_infrastructure_technical</t>
-  </si>
-  <si>
-    <t>AI_Grading_Plan_Assistant</t>
-  </si>
-  <si>
-    <t>AI Grading Plans</t>
-  </si>
-  <si>
-    <t>AI_test_framework</t>
-  </si>
-  <si>
-    <t>archival_automation</t>
-  </si>
-  <si>
-    <t>autogen</t>
-  </si>
-  <si>
-    <t>automated_application_launcher</t>
-  </si>
-  <si>
-    <t>calculator</t>
-  </si>
-  <si>
-    <t>cancer_care_timeline</t>
-  </si>
-  <si>
-    <t>cancer_treatment_outcomes</t>
-  </si>
-  <si>
-    <t>cancer_treatment_side_effects</t>
-  </si>
-  <si>
-    <t>chat_gpt_integration</t>
-  </si>
-  <si>
-    <t>choropleth_map</t>
-  </si>
-  <si>
-    <t>chronic_disease_registry</t>
-  </si>
-  <si>
-    <t>clinical_classification_system</t>
-  </si>
-  <si>
-    <t>Common_Skiing_Injuries</t>
-  </si>
-  <si>
-    <t>configuring_settings</t>
-  </si>
-  <si>
-    <t>convert_msaccess</t>
-  </si>
-  <si>
-    <t>corpus</t>
-  </si>
-  <si>
-    <t>correlation_heatmap</t>
-  </si>
-  <si>
-    <t>create_readme_md</t>
-  </si>
-  <si>
-    <t>create_sign</t>
-  </si>
-  <si>
-    <t>create_solution_definition</t>
-  </si>
-  <si>
-    <t>create_solution_sign</t>
-  </si>
-  <si>
-    <t>create_solution_word_cloud</t>
-  </si>
-  <si>
-    <t>curated_datasets</t>
-  </si>
-  <si>
-    <t>daily_data_loader</t>
-  </si>
-  <si>
-    <t>data_cleansing</t>
-  </si>
-  <si>
-    <t>data_delta_calculator</t>
-  </si>
-  <si>
-    <t>data_discovery</t>
-  </si>
-  <si>
-    <t>data_loader_reference_tables</t>
-  </si>
-  <si>
-    <t>data_loader_transactional__tables</t>
-  </si>
-  <si>
-    <t>data_profiling</t>
-  </si>
-  <si>
-    <t>data_science_report_generator</t>
-  </si>
-  <si>
-    <t>data_sets</t>
-  </si>
-  <si>
-    <t>DB_Analysis</t>
-  </si>
-  <si>
-    <t>DB_Discovery</t>
-  </si>
-  <si>
-    <t>descriptive_statistics</t>
-  </si>
-  <si>
-    <t>design_goal</t>
-  </si>
-  <si>
-    <t>diabetes_outcome_analysis</t>
-  </si>
-  <si>
-    <t>diabetes_risk_stratification</t>
-  </si>
-  <si>
-    <t>disease_progression_model</t>
-  </si>
-  <si>
-    <t>docling</t>
-  </si>
-  <si>
-    <t>domain_topic_classifier</t>
-  </si>
-  <si>
-    <t>email_automation</t>
-  </si>
-  <si>
-    <t>environment_testing</t>
-  </si>
-  <si>
-    <t>epidemiology_methodology</t>
-  </si>
-  <si>
-    <t>file_discovery</t>
-  </si>
-  <si>
-    <t>file_manager</t>
-  </si>
-  <si>
-    <t>file_removal</t>
-  </si>
-  <si>
-    <t>file_watchdog</t>
-  </si>
-  <si>
-    <t>form_validator</t>
-  </si>
-  <si>
-    <t>getting_started_with_django</t>
-  </si>
-  <si>
-    <t>git_commands</t>
-  </si>
-  <si>
-    <t>github_automation</t>
-  </si>
-  <si>
-    <t>glossary_term</t>
-  </si>
-  <si>
-    <t>happiness_datasets</t>
-  </si>
-  <si>
-    <t>high_risk_high_need</t>
-  </si>
-  <si>
-    <t>hole_in_one</t>
-  </si>
-  <si>
-    <t>HTML_to_document</t>
-  </si>
-  <si>
-    <t>hugging_face_transformers</t>
-  </si>
-  <si>
-    <t>incremental_imports</t>
-  </si>
-  <si>
-    <t>infrastructure_setup</t>
-  </si>
-  <si>
-    <t>intelligent_chatbot_corpus_learning</t>
-  </si>
-  <si>
-    <t>intelligent_chatbot_data_serialization</t>
-  </si>
-  <si>
-    <t>intelligent_chatbot_generative_digital_assistant</t>
-  </si>
-  <si>
-    <t>intelligent_chatbot_web_scrapping</t>
-  </si>
-  <si>
-    <t>introduction_to_pandas</t>
-  </si>
-  <si>
-    <t>kids_abc_book</t>
-  </si>
-  <si>
-    <t>Knowledge_Transfer_Solution</t>
-  </si>
-  <si>
-    <t>LangGraph</t>
-  </si>
-  <si>
-    <t>library_installer</t>
-  </si>
-  <si>
-    <t>quick_logger</t>
-  </si>
-  <si>
-    <t>logging_and_debugging</t>
-  </si>
-  <si>
-    <t>magic_classifier</t>
-  </si>
-  <si>
-    <t>managing_personas</t>
-  </si>
-  <si>
-    <t>membership_matching</t>
-  </si>
-  <si>
-    <t>microsoft_azure</t>
-  </si>
-  <si>
-    <t>MidasTouch</t>
-  </si>
-  <si>
-    <t>nlp_to_sql_training_data_builder</t>
-  </si>
-  <si>
-    <t>notebook_clone</t>
-  </si>
-  <si>
-    <t>oncology_procedures_classification</t>
-  </si>
-  <si>
-    <t>oncology_terminology</t>
-  </si>
-  <si>
-    <t>patient_complexity_index</t>
-  </si>
-  <si>
-    <t>patient_word_cloud</t>
-  </si>
-  <si>
-    <t>penguins</t>
-  </si>
-  <si>
-    <t>poor_emotional_regulatory_control</t>
-  </si>
-  <si>
-    <t>precision_oncology</t>
-  </si>
-  <si>
-    <t>predicting_breast_cancer</t>
-  </si>
-  <si>
-    <t>predicting_colorectal_cancer</t>
-  </si>
-  <si>
-    <t>predicting_diabetes</t>
-  </si>
-  <si>
-    <t>predicting_lung_cancer</t>
-  </si>
-  <si>
-    <t>principal_component_analysis</t>
-  </si>
-  <si>
-    <t>producing_the_voice_over</t>
-  </si>
-  <si>
-    <t>progress_bar</t>
-  </si>
-  <si>
-    <t>python_foundation</t>
-  </si>
-  <si>
-    <t>registering_library_to_pypi</t>
-  </si>
-  <si>
-    <t>remote_process_automation_excel</t>
-  </si>
-  <si>
-    <t>research_canvas</t>
-  </si>
-  <si>
-    <t>rules_engine</t>
-  </si>
-  <si>
-    <t>sqlite_introduction</t>
-  </si>
-  <si>
-    <t>simple_chatbot_simple_nlp_response</t>
-  </si>
-  <si>
-    <t>smart_mini_proposal</t>
-  </si>
-  <si>
-    <t>solution_registry</t>
-  </si>
-  <si>
-    <t>supervised_learning</t>
-  </si>
-  <si>
-    <t>system_information</t>
-  </si>
-  <si>
-    <t>talking_code</t>
-  </si>
-  <si>
-    <t>task_scheduling</t>
-  </si>
-  <si>
-    <t>ThriveAI</t>
-  </si>
-  <si>
-    <t>unzip_automation</t>
-  </si>
-  <si>
-    <t>update_solution_images</t>
-  </si>
-  <si>
-    <t>updating_libraries</t>
-  </si>
-  <si>
-    <t>web_automation</t>
-  </si>
-  <si>
-    <t>word_cloud</t>
-  </si>
-  <si>
-    <t>world_mood</t>
-  </si>
-  <si>
-    <t>AI_chatbot_scorecard</t>
-  </si>
-  <si>
-    <t>Produce high quality prompts to get the most out of AI.</t>
-  </si>
-  <si>
-    <t>A sophisticated AI infrastructure that uses AI agents and LLMs to research an query population health data.</t>
-  </si>
-  <si>
-    <t>Use uagent to Create AI agents to perform workflows and LLM integrations.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI chatbot using LLMS and RAG to ethically answer questions about private enterprise data </t>
-  </si>
-  <si>
-    <t>Utilizing an AI Assistant in innovative ways to enhance the civil engineering process of grading a property.</t>
-  </si>
-  <si>
-    <t>Utilizing AI in innovative ways to enhance the civil engineering process of grading a property.</t>
-  </si>
-  <si>
-    <t>Establishes infrastructure for testing AI platform.</t>
-  </si>
-  <si>
-    <t>Archival Automation automatically backs up your data and puts a archive  stamp on it.</t>
-  </si>
-  <si>
-    <t>User and password authentication</t>
-  </si>
-  <si>
-    <t>Use autogen AI agents to perform workflows and LLM integrations.</t>
-  </si>
-  <si>
-    <t>Automated Application Launcher launches any application you want on a schedule or through voice commands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Build a simple calculator using python and tkinter to enhance your programming skills </t>
-  </si>
-  <si>
-    <t>Analyzing each patients temporal pathway through their cancer treatment and survivorship.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Provides a list of measurable outcomes for Cancer Care including remission, ongoing treatment, active surveillance, death, etc.  </t>
-  </si>
-  <si>
-    <t>quantifying of side affects associated with major cancer treatment modalities</t>
-  </si>
-  <si>
-    <t>Solution that demonstrates how to integrate your applications with **Chat GPT**. Utilizes the API to integrate with the LLM **Large Language Model**</t>
-  </si>
-  <si>
-    <t>Mapping solution for global and local choropleth maps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A chronic disease registry classifies patients with specific diseases or conditions. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">This solution extends and enhances the ICD-10-CM diagnosis standard to include disease classifications that can be used for registries and care outreach. </t>
-  </si>
-  <si>
-    <t>A list of common skiing injuries a National Ski Patrol person may face.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solution for Configuring Settings. The config.ini file in Python serves as a centralized repository for storing configuration parameters, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solution for converting MS access into a new technology stack. </t>
-  </si>
-  <si>
-    <t>Provide a set of images designed to brand and represent each unique solution.</t>
-  </si>
-  <si>
-    <t>A correlation heatmap provides insights to critical relationships within Data</t>
-  </si>
-  <si>
-    <t>Generate a beautiful and effective readme.md file.</t>
-  </si>
-  <si>
-    <t>A tiny utility to create PNG signs.</t>
-  </si>
-  <si>
-    <t>A utility to create a new definition  for every solution.</t>
-  </si>
-  <si>
-    <t>A utility to create a new PNG sign for every solution.</t>
-  </si>
-  <si>
-    <t>A utility to create a word cloud for every solution.</t>
-  </si>
-  <si>
-    <t>Solution for Curated Datasets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load a the LATEST DELTA of NEW TRANSACTIONS  into a relational datastore. Run periodically for freshness. </t>
-  </si>
-  <si>
-    <t>A story board document of data amalysis from start to finish.</t>
-  </si>
-  <si>
-    <t>A set of utilities to easily cleans and improve your data</t>
-  </si>
-  <si>
-    <t>Calculates the structural difference between raw data sources. Compares to LAST LOAD to determine what is NEW. This is for loading data incrementally over time so that history isn't constantly re-loaded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finds ALL the valuable data assets on your system and registers them. </t>
-  </si>
-  <si>
-    <t>Load a series of reference tables into a relational datastore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load a large historical transactional tables into a relational datastore. One Time LOAD </t>
-  </si>
-  <si>
-    <t>Tells you **EVERYTHING** about your data.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This project creates a word document for data science projects that produces a report of the scientific </t>
-  </si>
-  <si>
-    <t>A repository of curated datasets for data science projects</t>
-  </si>
-  <si>
-    <t>Perform database analysis on ANY database to generate the schema and Data Discription Language.</t>
-  </si>
-  <si>
-    <t>Perform database discovery on ANY database to generate the Schema and Data Discription Language.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">process used to analyze the data. </t>
-  </si>
-  <si>
-    <t>A analysis of outcomes related to diabetes treatments</t>
-  </si>
-  <si>
-    <t>Machine Learning Risk stratification - 3 different approaches</t>
-  </si>
-  <si>
-    <t>Solution for Disease Progression Model</t>
-  </si>
-  <si>
-    <t>Utilize docling to build a knowledge base out of ANY document so an AI LLM query the data</t>
-  </si>
-  <si>
-    <t>identify the most likely knowledge domain and topic based upon keywords</t>
-  </si>
-  <si>
-    <t>Solution for Email Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Makes sure all your computing resources are ready to perform complex workflows. </t>
-  </si>
-  <si>
-    <t>The epidemiology methodology establishes a versatile data science methodology for epidemiology projects spanning various conditions or diseases The approach begins with comprehensive data collection, encompassing demographics, environmental factors, and relevant health metrics. Employing advanced statistical analyses and machine learning algorithms, the methodology aims to discern patterns, identify risk factors, and optimize predictive models, fostering a holistic understanding of the factors influencing the studied health outcomes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discovers where your critical data is and provides archives. </t>
-  </si>
-  <si>
-    <t>Solution for File Manager</t>
-  </si>
-  <si>
-    <t>Solution for File Removal</t>
-  </si>
-  <si>
-    <t>Solution for File Watchdog</t>
-  </si>
-  <si>
-    <t>Solution for Form Validator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git allows you to quickly download pre-built solutions  </t>
-  </si>
-  <si>
-    <t>Git is a distributed version control system designed to track changes in source code during software development.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">glossary of terms </t>
-  </si>
-  <si>
-    <t>A utility to create a word document docx out of HTML documents.</t>
-  </si>
-  <si>
-    <t>A proven holistic approach to a better life with greater happiness.</t>
-  </si>
-  <si>
-    <t>[5]:</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># Calculate and classify the process performance </t>
-  </si>
-  <si>
-    <t>status = ql.calculate_process_performance(solution_name, start_time)</t>
-  </si>
-  <si>
-    <t>print(ql.append_log_file(solution_name))</t>
-  </si>
-  <si>
-    <t>Pandas is a powerful Python library used for data manipulation and analysis.</t>
-  </si>
-  <si>
-    <t>2024-03-15 10:39:07,381 - INFO - START solution_temple Start Time = 2024-03-15 10:39:07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Knowledge Transfer for AI Solutions - Transfering REPOS. </t>
-  </si>
-  <si>
-    <t>Orchestrate Agentic AI with LangGraph and LangChain</t>
-  </si>
-  <si>
-    <t>2024-03-15 10:39:07,381 - INFO - solution_temple Step 0 - Initialize the configuration file parser</t>
-  </si>
-  <si>
-    <t>2024-03-15 10:39:07,382 - INFO - Process solution_temple Step 0 - Initializing and starting Logging Process.</t>
-  </si>
-  <si>
-    <t>2024-03-15 10:39:07,391 - INFO - PERFORMANCE solution_temple The total process duration was:0.01</t>
-  </si>
-  <si>
-    <t>identify if a magic command is found if chat input based upon magic keywords</t>
-  </si>
-  <si>
-    <t>2024-03-15 10:39:07,391 - INFO - PERFORMANCE solution_temple Stop Time = 2024-03-15 10:39:07</t>
-  </si>
-  <si>
-    <t>A utility to create a web page HTML out of mark down documents.</t>
-  </si>
-  <si>
-    <t>2024-03-15 10:39:07,391 - INFO - PERFORMANCE solution_temple Short process duration less than 3 Seconds:0.01</t>
-  </si>
-  <si>
-    <t>A learning pathway for microsoft azure AI fundamentals.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning how to trade GOLD futures </t>
-  </si>
-  <si>
-    <t>2024-03-15 10:39:07,391 - INFO - PERFORMANCE solution_temple Performance optimization is not reccomended</t>
-  </si>
-  <si>
-    <t>establishes training data for AI chatbot</t>
-  </si>
-  <si>
-    <t>2024-03-15 10:39:07,391 - INFO - END solution_temple =============================================</t>
-  </si>
-  <si>
-    <t>Click to add a cell.</t>
-  </si>
-  <si>
-    <t>Solution for Patient Word Cloud</t>
-  </si>
-  <si>
-    <t>Solution for Penguins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calculation and stratification of Risk based upon survey (BRFSS) of specific control behaviors (eating disorders, binge dirking, or substance abuse </t>
-  </si>
-  <si>
-    <t>Analysis of needs for current state of precision oncology.</t>
-  </si>
-  <si>
-    <t>Machine learning for predicting breast cancer.</t>
-  </si>
-  <si>
-    <t>Machine learning for predicting colorectal cancer.</t>
-  </si>
-  <si>
-    <t>Machine learning for predicting diabetes.</t>
-  </si>
-  <si>
-    <t>Machine learning for predicting lung cancer.</t>
-  </si>
-  <si>
-    <t>Solution for Principal Component Analysis</t>
-  </si>
-  <si>
-    <t>Converts solution documentation to MP3 audio for voice over</t>
-  </si>
-  <si>
-    <t>Solution for Progress Bar</t>
-  </si>
-  <si>
-    <t>Solution for Python Foundation</t>
-  </si>
-  <si>
-    <t>Register your python libraries to pypi to make them pip and uv installable</t>
-  </si>
-  <si>
-    <t>Makes excel files pretty, more functional , and easier to use.  This one solution saves hours !!!!</t>
-  </si>
-  <si>
-    <t>Utilizing an AI Assistant to create re usable research workflows and pathways. research canvas to collaborate and share work</t>
-  </si>
-  <si>
-    <t>Automated rules engine for dynamically analyzing data quality.</t>
-  </si>
-  <si>
-    <t>SQLite introduction provides an introduction to SQL lite</t>
-  </si>
-  <si>
-    <t>OLD SCHOOL Chatbot- Like LEXI of olden days with pre-built response lexicon …. But with advanced natural language built in.</t>
-  </si>
-  <si>
-    <t>Creates a mini proposal using a template and SMART criteria.</t>
-  </si>
-  <si>
-    <t>Solution Registry - houses a list of solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streamlit UI for analytics catalogue </t>
-  </si>
-  <si>
-    <t xml:space="preserve">A very tiny example of supervised learning. </t>
-  </si>
-  <si>
-    <t>Provides general system information including CURRENT  memory / CPU usage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application for building sophisticated text to speech </t>
-  </si>
-  <si>
-    <t>Schedules tasks and executes runtimes</t>
-  </si>
-  <si>
-    <t>Empowering organizations to harness the transformative potential of artificial intelligence</t>
-  </si>
-  <si>
-    <t>Solution for Unzip Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Makes sure the LATEST technology is used. </t>
-  </si>
-  <si>
-    <t>Solution for Web Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produces a word cloud using the3 most relevant terminology using whatever cloud shape is supplied. </t>
-  </si>
-  <si>
-    <t>Solution for World Mood</t>
-  </si>
-  <si>
-    <t>The 7 Layer System Response Score is a comprehensive, domain specific evaluation framework that rates chatbot responses from 0 to 100.</t>
-  </si>
-  <si>
-    <t>This solution automates creating python script to run in windows task scheduler.</t>
-  </si>
-  <si>
-    <t>chatbot that uses Natural language processing NLP to  learn from a specified corpus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Template for kick starting sophisticated python projects </t>
-  </si>
-  <si>
-    <t>A story board document of data analysis from start to finish.</t>
-  </si>
-  <si>
-    <t>Streamlit app for editing and persisting changes to data</t>
-  </si>
-  <si>
-    <t>A repository for diagrams</t>
-  </si>
-  <si>
-    <t>This solution includes a set of Ethical Guardrails designed to detect and prevent inappropriate, biased, or harmful outputs from AI systems.</t>
-  </si>
-  <si>
-    <t>Generates SQL templates for Datasets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analyze the Internation Classification of Disease ICD-10-CM </t>
-  </si>
-  <si>
-    <t>Identify the multidisciplinary cancer care team roles and responsibilities in cancer treatment.</t>
-  </si>
-  <si>
-    <t>Define and classify diagnosis for all forms of cancer.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Epidemiology methodology for oncology </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solution for calculating  patients lieklihood to develop cancer within the next year. </t>
-  </si>
-  <si>
-    <t>A report on specific patients gaps in care</t>
-  </si>
-  <si>
-    <t>Calculated index of monthly life quality from initial (denovo) diagnosis of major disease</t>
-  </si>
-  <si>
-    <t>Machine learning with Taipy web GUI and tensorflow ML</t>
-  </si>
-  <si>
-    <t>TF-IDF helps identify important terms within a document by giving higher weights to terms that are frequent in the document but rare in the corpus</t>
-  </si>
-  <si>
-    <t>Tells you **EVERYTHING** about your data…  **easily** discover any issues in your data</t>
-  </si>
-  <si>
-    <t>Descriptive statistics summarize and describe the main features of a dataset through measures such as mean, median, mode, standard deviation, and visualizations.</t>
-  </si>
-  <si>
-    <t>A repository  for Happiness Datasets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automates triage of high risk - high need patients </t>
-  </si>
-  <si>
-    <t>Solution for Hugging Face Transformers</t>
-  </si>
-  <si>
-    <t>Solution for Incremental Imports</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> This solution establishes an Infrastructure Directory to copy, secure. maintain, and archive All of your work in progress.  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chatbot instantly scrapes reads any corpus or dataset. Learns it and provides a conversation about it. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chatbot instantly scrapes reads any relational datastore, excel spreadsheet and segmentizes it. Uses NLP to for paragraphs and answer in natural language.  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chatbot Assistant performs almost ANY task you can think of. This is your custom "Alexa" it opens mail, formats excel sheets, reads to you, tells jokes, and writes a swimming program for you.  Embedded ChatGPT 4. </t>
-  </si>
-  <si>
-    <t>Chatbot instantly scrapes your or anyone else's website. Learns it and provides a conversation about it. Use this to digitally engage your clients.</t>
-  </si>
-  <si>
-    <t>Solution for Kids ABC Book</t>
-  </si>
-  <si>
-    <t>Solution for Library Installer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.py library for easily using logging and debugging. </t>
-  </si>
-  <si>
-    <t>Solution for Logging And Debugging</t>
-  </si>
-  <si>
-    <t>Generate and manage personas of any type to Make Chat GPT even MORE AMAZING !!!!</t>
-  </si>
-  <si>
-    <t>Solution for Membership Matching</t>
-  </si>
-  <si>
-    <t>Solution for Notebook Clone</t>
-  </si>
-  <si>
-    <t>Process for classifying oncology procedures.</t>
-  </si>
-  <si>
-    <t>A dictionary of oncology  terminology.</t>
-  </si>
-  <si>
-    <t>Analyzing each patients risk for developing cancer within next year.</t>
-  </si>
-  <si>
-    <t>Solution for calculating a patients complexity based upon their diagnostic profile.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calculation and stratification of Risk based upon survey (BRFSS) of specific control behaviors (eating disorders, binge drinking, or substance abuse </t>
-  </si>
-  <si>
-    <t>sqlite_introduction provides an introduction to SQL lite</t>
-  </si>
-  <si>
-    <t>The 7 Layer System Response Score is a comprehensive, domain specific evaluation framework that rates chatbot responses from 0 to 100.</t>
   </si>
 </sst>
 </file>
@@ -1337,10 +1381,8 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1401,9 +1443,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1441,7 +1483,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1475,7 +1517,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1510,10 +1551,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1687,8 +1727,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D150"/>
-  <sheetFormatPr defaultColWidth="77.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D158"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="255.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -1709,2037 +1754,2149 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>153</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>273</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>273</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>274</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>274</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>154</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>275</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>275</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>155</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>276</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>276</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>156</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>274</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>274</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>157</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>274</v>
+        <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>274</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>158</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>277</v>
+        <v>5</v>
       </c>
       <c r="D8" t="s">
-        <v>277</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>159</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>278</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>160</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>279</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>279</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>161</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>280</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>280</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>281</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>281</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>162</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>282</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>282</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>163</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>283</v>
+        <v>35</v>
       </c>
       <c r="D14" t="s">
-        <v>283</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>164</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>284</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>284</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>165</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>285</v>
+        <v>41</v>
       </c>
       <c r="D16" t="s">
-        <v>285</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>166</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>286</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>286</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>167</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>287</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
-        <v>287</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
-        <v>168</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>288</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>288</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>169</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
-        <v>289</v>
+        <v>53</v>
       </c>
       <c r="D20" t="s">
-        <v>295</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>170</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s">
-        <v>290</v>
+        <v>56</v>
       </c>
       <c r="D21" t="s">
-        <v>290</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="B22" t="s">
-        <v>171</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
-        <v>291</v>
+        <v>59</v>
       </c>
       <c r="D22" t="s">
-        <v>291</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="B23" t="s">
-        <v>172</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s">
-        <v>292</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s">
-        <v>292</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="B24" t="s">
-        <v>173</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s">
-        <v>293</v>
+        <v>66</v>
       </c>
       <c r="D24" t="s">
-        <v>293</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="B25" t="s">
-        <v>174</v>
+        <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>294</v>
+        <v>69</v>
       </c>
       <c r="D25" t="s">
-        <v>294</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="B26" t="s">
-        <v>175</v>
+        <v>71</v>
       </c>
       <c r="C26" t="s">
-        <v>295</v>
+        <v>72</v>
       </c>
       <c r="D26" t="s">
-        <v>295</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>176</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>296</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s">
-        <v>296</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="B28" t="s">
-        <v>177</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s">
-        <v>297</v>
+        <v>78</v>
       </c>
       <c r="D28" t="s">
-        <v>297</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="B29" t="s">
-        <v>178</v>
+        <v>80</v>
       </c>
       <c r="C29" t="s">
-        <v>298</v>
+        <v>63</v>
       </c>
       <c r="D29" t="s">
-        <v>298</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="B30" t="s">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="C30" t="s">
-        <v>299</v>
+        <v>83</v>
       </c>
       <c r="D30" t="s">
-        <v>299</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="B31" t="s">
-        <v>180</v>
+        <v>85</v>
       </c>
       <c r="C31" t="s">
-        <v>300</v>
+        <v>86</v>
       </c>
       <c r="D31" t="s">
-        <v>300</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="B32" t="s">
-        <v>181</v>
+        <v>88</v>
       </c>
       <c r="C32" t="s">
-        <v>301</v>
+        <v>89</v>
       </c>
       <c r="D32" t="s">
-        <v>301</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="B33" t="s">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="C33" t="s">
-        <v>302</v>
+        <v>92</v>
       </c>
       <c r="D33" t="s">
-        <v>302</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="B34" t="s">
-        <v>183</v>
+        <v>94</v>
       </c>
       <c r="C34" t="s">
-        <v>303</v>
+        <v>95</v>
       </c>
       <c r="D34" t="s">
-        <v>303</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="B35" t="s">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="C35" t="s">
-        <v>304</v>
+        <v>98</v>
       </c>
       <c r="D35" t="s">
-        <v>304</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="B36" t="s">
-        <v>184</v>
+        <v>100</v>
       </c>
       <c r="C36" t="s">
-        <v>305</v>
+        <v>101</v>
       </c>
       <c r="D36" t="s">
-        <v>305</v>
+        <v>101</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>39</v>
+        <v>102</v>
       </c>
       <c r="B37" t="s">
-        <v>185</v>
+        <v>103</v>
       </c>
       <c r="C37" t="s">
-        <v>306</v>
+        <v>104</v>
       </c>
       <c r="D37" t="s">
-        <v>306</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="B38" t="s">
-        <v>186</v>
+        <v>106</v>
       </c>
       <c r="C38" t="s">
-        <v>307</v>
+        <v>107</v>
       </c>
       <c r="D38" t="s">
-        <v>307</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>108</v>
       </c>
       <c r="B39" t="s">
-        <v>187</v>
+        <v>109</v>
       </c>
       <c r="C39" t="s">
-        <v>308</v>
+        <v>110</v>
       </c>
       <c r="D39" t="s">
-        <v>308</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>42</v>
+        <v>111</v>
       </c>
       <c r="B40" t="s">
-        <v>188</v>
+        <v>112</v>
       </c>
       <c r="C40" t="s">
-        <v>309</v>
+        <v>113</v>
       </c>
       <c r="D40" t="s">
-        <v>309</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>114</v>
       </c>
       <c r="B41" t="s">
-        <v>189</v>
+        <v>115</v>
       </c>
       <c r="C41" t="s">
-        <v>310</v>
+        <v>116</v>
       </c>
       <c r="D41" t="s">
-        <v>404</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>117</v>
       </c>
       <c r="B42" t="s">
-        <v>190</v>
+        <v>118</v>
       </c>
       <c r="C42" t="s">
-        <v>311</v>
+        <v>119</v>
+      </c>
+      <c r="D42" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="B43" t="s">
-        <v>191</v>
+        <v>121</v>
       </c>
       <c r="C43" t="s">
-        <v>312</v>
+        <v>122</v>
       </c>
       <c r="D43" t="s">
-        <v>312</v>
+        <v>122</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>46</v>
+        <v>123</v>
       </c>
       <c r="B44" t="s">
-        <v>192</v>
+        <v>124</v>
       </c>
       <c r="C44" t="s">
-        <v>313</v>
+        <v>125</v>
       </c>
       <c r="D44" t="s">
-        <v>313</v>
+        <v>126</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="B45" t="s">
-        <v>193</v>
+        <v>128</v>
       </c>
       <c r="C45" t="s">
-        <v>314</v>
-      </c>
-      <c r="D45" t="s">
-        <v>314</v>
+        <v>129</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="B46" t="s">
-        <v>194</v>
+        <v>131</v>
       </c>
       <c r="C46" t="s">
-        <v>315</v>
+        <v>132</v>
       </c>
       <c r="D46" t="s">
-        <v>405</v>
+        <v>132</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>49</v>
+        <v>133</v>
       </c>
       <c r="B47" t="s">
-        <v>195</v>
+        <v>134</v>
       </c>
       <c r="C47" t="s">
-        <v>49</v>
+        <v>135</v>
+      </c>
+      <c r="D47" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>50</v>
+        <v>136</v>
       </c>
       <c r="B48" t="s">
-        <v>196</v>
+        <v>137</v>
       </c>
       <c r="C48" t="s">
-        <v>316</v>
+        <v>138</v>
+      </c>
+      <c r="D48" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>51</v>
+        <v>139</v>
       </c>
       <c r="B49" t="s">
-        <v>197</v>
+        <v>140</v>
       </c>
       <c r="C49" t="s">
-        <v>317</v>
+        <v>141</v>
+      </c>
+      <c r="D49" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>52</v>
+        <v>143</v>
       </c>
       <c r="B50" t="s">
-        <v>198</v>
+        <v>144</v>
       </c>
       <c r="C50" t="s">
-        <v>318</v>
+        <v>143</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="B51" t="s">
-        <v>199</v>
+        <v>146</v>
       </c>
       <c r="C51" t="s">
-        <v>319</v>
-      </c>
-      <c r="D51" t="s">
-        <v>319</v>
+        <v>147</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="B52" t="s">
-        <v>200</v>
+        <v>149</v>
       </c>
       <c r="C52" t="s">
-        <v>320</v>
-      </c>
-      <c r="D52" t="s">
-        <v>320</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>55</v>
+        <v>151</v>
       </c>
       <c r="B53" t="s">
-        <v>201</v>
+        <v>152</v>
       </c>
       <c r="C53" t="s">
-        <v>321</v>
+        <v>153</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>56</v>
+        <v>154</v>
       </c>
       <c r="B54" t="s">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="C54" t="s">
-        <v>322</v>
+        <v>156</v>
+      </c>
+      <c r="D54" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>57</v>
+        <v>157</v>
       </c>
       <c r="B55" t="s">
-        <v>203</v>
+        <v>158</v>
       </c>
       <c r="C55" t="s">
-        <v>323</v>
+        <v>159</v>
+      </c>
+      <c r="D55" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="B56" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="C56" t="s">
-        <v>324</v>
+        <v>162</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>59</v>
+        <v>163</v>
       </c>
       <c r="B57" t="s">
-        <v>205</v>
+        <v>164</v>
       </c>
       <c r="C57" t="s">
-        <v>325</v>
+        <v>165</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>60</v>
+        <v>166</v>
       </c>
       <c r="B58" t="s">
-        <v>206</v>
+        <v>167</v>
       </c>
       <c r="C58" t="s">
-        <v>326</v>
+        <v>168</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>61</v>
+        <v>169</v>
       </c>
       <c r="B59" t="s">
-        <v>207</v>
+        <v>170</v>
       </c>
       <c r="C59" t="s">
-        <v>327</v>
+        <v>171</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>62</v>
+        <v>172</v>
       </c>
       <c r="B60" t="s">
-        <v>208</v>
+        <v>173</v>
       </c>
       <c r="C60" t="s">
-        <v>328</v>
+        <v>174</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>63</v>
+        <v>175</v>
       </c>
       <c r="B61" t="s">
-        <v>209</v>
+        <v>176</v>
       </c>
       <c r="C61" t="s">
-        <v>329</v>
+        <v>177</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>64</v>
+        <v>178</v>
       </c>
       <c r="B62" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="C62" t="s">
-        <v>329</v>
+        <v>180</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>65</v>
+        <v>181</v>
       </c>
       <c r="B63" t="s">
-        <v>211</v>
+        <v>182</v>
       </c>
       <c r="C63" t="s">
-        <v>330</v>
+        <v>183</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>66</v>
+        <v>184</v>
       </c>
       <c r="B64" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="C64" t="s">
-        <v>331</v>
+        <v>186</v>
+      </c>
+      <c r="D64" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>67</v>
+        <v>187</v>
       </c>
       <c r="B65" t="s">
-        <v>67</v>
+        <v>188</v>
       </c>
       <c r="C65" t="s">
-        <v>332</v>
-      </c>
-      <c r="D65" t="s">
-        <v>332</v>
+        <v>189</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>68</v>
+        <v>190</v>
       </c>
       <c r="B66" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="C66" t="s">
-        <v>213</v>
-      </c>
-      <c r="D66" t="s">
-        <v>406</v>
+        <v>189</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>69</v>
+        <v>192</v>
       </c>
       <c r="B67" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="C67" t="s">
-        <v>214</v>
-      </c>
-      <c r="D67" t="s">
-        <v>407</v>
+        <v>194</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>70</v>
+        <v>195</v>
       </c>
       <c r="B68" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="C68" t="s">
-        <v>333</v>
-      </c>
-      <c r="D68" t="s">
-        <v>333</v>
+        <v>197</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>71</v>
+        <v>198</v>
       </c>
       <c r="B69" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="C69" t="s">
-        <v>332</v>
+        <v>199</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>199</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>72</v>
+        <v>200</v>
       </c>
       <c r="B70" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="C70" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="D70" t="s">
-        <v>408</v>
+        <v>202</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>73</v>
+        <v>203</v>
       </c>
       <c r="B71" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C71" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="D71" t="s">
-        <v>409</v>
+        <v>205</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>74</v>
+        <v>206</v>
       </c>
       <c r="B72" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="C72" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="D72" t="s">
-        <v>410</v>
+        <v>208</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="B73" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C73" t="s">
-        <v>334</v>
+        <v>211</v>
       </c>
       <c r="D73" t="s">
-        <v>411</v>
+        <v>211</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>76</v>
+        <v>212</v>
       </c>
       <c r="B74" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C74" t="s">
-        <v>335</v>
+        <v>199</v>
       </c>
       <c r="D74" t="s">
-        <v>412</v>
+        <v>199</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>77</v>
+        <v>214</v>
       </c>
       <c r="B75" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="C75" t="s">
-        <v>336</v>
+        <v>215</v>
       </c>
       <c r="D75" t="s">
-        <v>413</v>
+        <v>216</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>78</v>
+        <v>217</v>
       </c>
       <c r="B76" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C76" t="s">
-        <v>337</v>
+        <v>218</v>
       </c>
       <c r="D76" t="s">
-        <v>414</v>
+        <v>219</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>79</v>
+        <v>220</v>
       </c>
       <c r="B77" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C77" t="s">
-        <v>338</v>
+        <v>221</v>
       </c>
       <c r="D77" t="s">
-        <v>338</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>80</v>
+        <v>223</v>
       </c>
       <c r="B78" t="s">
+        <v>224</v>
+      </c>
+      <c r="C78" t="s">
         <v>225</v>
       </c>
-      <c r="C78" t="s">
-        <v>339</v>
-      </c>
       <c r="D78" t="s">
-        <v>415</v>
+        <v>226</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>81</v>
+        <v>227</v>
       </c>
       <c r="B79" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C79" t="s">
-        <v>340</v>
+        <v>229</v>
       </c>
       <c r="D79" t="s">
-        <v>340</v>
+        <v>230</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>82</v>
+        <v>231</v>
       </c>
       <c r="B80" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C80" t="s">
-        <v>341</v>
+        <v>233</v>
       </c>
       <c r="D80" t="s">
-        <v>341</v>
+        <v>234</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>83</v>
+        <v>235</v>
       </c>
       <c r="B81" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C81" t="s">
-        <v>342</v>
+        <v>237</v>
       </c>
       <c r="D81" t="s">
-        <v>416</v>
+        <v>238</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>84</v>
+        <v>239</v>
       </c>
       <c r="B82" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="C82" t="s">
-        <v>343</v>
+        <v>241</v>
       </c>
       <c r="D82" t="s">
-        <v>417</v>
+        <v>241</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>85</v>
+        <v>242</v>
       </c>
       <c r="B83" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="C83" t="s">
-        <v>344</v>
+        <v>244</v>
       </c>
       <c r="D83" t="s">
-        <v>418</v>
+        <v>245</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>86</v>
+        <v>246</v>
       </c>
       <c r="B84" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="C84" t="s">
-        <v>345</v>
+        <v>248</v>
       </c>
       <c r="D84" t="s">
-        <v>345</v>
+        <v>248</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>87</v>
+        <v>249</v>
       </c>
       <c r="B85" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="C85" t="s">
-        <v>346</v>
+        <v>251</v>
       </c>
       <c r="D85" t="s">
-        <v>419</v>
+        <v>251</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>88</v>
+        <v>252</v>
       </c>
       <c r="B86" t="s">
-        <v>142</v>
+        <v>253</v>
       </c>
       <c r="C86" t="s">
-        <v>347</v>
+        <v>254</v>
       </c>
       <c r="D86" t="s">
-        <v>347</v>
+        <v>255</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>89</v>
+        <v>256</v>
       </c>
       <c r="B87" t="s">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="C87" t="s">
-        <v>348</v>
+        <v>258</v>
       </c>
       <c r="D87" t="s">
-        <v>420</v>
+        <v>259</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>90</v>
+        <v>260</v>
       </c>
       <c r="B88" t="s">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="C88" t="s">
-        <v>349</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>349</v>
+        <v>263</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>91</v>
+        <v>264</v>
       </c>
       <c r="B89" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="C89" t="s">
-        <v>350</v>
+        <v>266</v>
       </c>
       <c r="D89" t="s">
-        <v>350</v>
+        <v>266</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>92</v>
+        <v>267</v>
       </c>
       <c r="B90" t="s">
-        <v>143</v>
+        <v>268</v>
       </c>
       <c r="C90" t="s">
-        <v>351</v>
+        <v>269</v>
       </c>
       <c r="D90" t="s">
-        <v>396</v>
+        <v>270</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>93</v>
+        <v>271</v>
       </c>
       <c r="B91" t="s">
-        <v>236</v>
+        <v>272</v>
       </c>
       <c r="C91" t="s">
-        <v>352</v>
+        <v>273</v>
       </c>
       <c r="D91" t="s">
-        <v>352</v>
+        <v>273</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>94</v>
+        <v>274</v>
       </c>
       <c r="B92" t="s">
-        <v>237</v>
+        <v>275</v>
       </c>
       <c r="C92" t="s">
-        <v>353</v>
+        <v>276</v>
       </c>
       <c r="D92" t="s">
-        <v>421</v>
+        <v>277</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>95</v>
+        <v>278</v>
       </c>
       <c r="B93" t="s">
-        <v>238</v>
+        <v>279</v>
       </c>
       <c r="C93" t="s">
-        <v>238</v>
+        <v>280</v>
       </c>
       <c r="D93" t="s">
-        <v>422</v>
+        <v>280</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>96</v>
+        <v>281</v>
       </c>
       <c r="B94" t="s">
-        <v>239</v>
+        <v>282</v>
       </c>
       <c r="C94" t="s">
-        <v>239</v>
+        <v>41</v>
       </c>
       <c r="D94" t="s">
-        <v>423</v>
+        <v>41</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>97</v>
+        <v>283</v>
       </c>
       <c r="B95" t="s">
-        <v>146</v>
+        <v>284</v>
       </c>
       <c r="C95" t="s">
-        <v>146</v>
+        <v>285</v>
       </c>
       <c r="D95" t="s">
-        <v>424</v>
+        <v>286</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>98</v>
+        <v>287</v>
       </c>
       <c r="B96" t="s">
-        <v>240</v>
+        <v>288</v>
       </c>
       <c r="C96" t="s">
-        <v>354</v>
+        <v>289</v>
       </c>
       <c r="D96" t="s">
-        <v>425</v>
+        <v>289</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>99</v>
+        <v>290</v>
       </c>
       <c r="B97" t="s">
-        <v>241</v>
+        <v>291</v>
       </c>
       <c r="C97" t="s">
-        <v>355</v>
+        <v>292</v>
       </c>
       <c r="D97" t="s">
-        <v>355</v>
+        <v>293</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>100</v>
+        <v>294</v>
       </c>
       <c r="B98" t="s">
-        <v>242</v>
+        <v>295</v>
       </c>
       <c r="C98" t="s">
-        <v>356</v>
+        <v>295</v>
       </c>
       <c r="D98" t="s">
-        <v>356</v>
+        <v>296</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>101</v>
+        <v>297</v>
       </c>
       <c r="B99" t="s">
-        <v>243</v>
+        <v>298</v>
       </c>
       <c r="C99" t="s">
-        <v>357</v>
+        <v>298</v>
       </c>
       <c r="D99" t="s">
-        <v>426</v>
+        <v>299</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>102</v>
+        <v>300</v>
       </c>
       <c r="B100" t="s">
-        <v>244</v>
+        <v>301</v>
       </c>
       <c r="C100" t="s">
-        <v>358</v>
+        <v>301</v>
       </c>
       <c r="D100" t="s">
-        <v>358</v>
+        <v>302</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>103</v>
+        <v>303</v>
       </c>
       <c r="B101" t="s">
-        <v>245</v>
+        <v>304</v>
       </c>
       <c r="C101" t="s">
-        <v>359</v>
+        <v>305</v>
       </c>
       <c r="D101" t="s">
-        <v>359</v>
+        <v>306</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>104</v>
+        <v>307</v>
       </c>
       <c r="B102" t="s">
-        <v>246</v>
+        <v>308</v>
       </c>
       <c r="C102" t="s">
-        <v>360</v>
+        <v>309</v>
       </c>
       <c r="D102" t="s">
-        <v>360</v>
+        <v>309</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>105</v>
+        <v>310</v>
       </c>
       <c r="B103" t="s">
-        <v>247</v>
+        <v>311</v>
       </c>
       <c r="C103" t="s">
-        <v>361</v>
+        <v>312</v>
       </c>
       <c r="D103" t="s">
-        <v>361</v>
+        <v>312</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>106</v>
+        <v>313</v>
       </c>
       <c r="B104" t="s">
-        <v>248</v>
+        <v>314</v>
       </c>
       <c r="C104" t="s">
-        <v>362</v>
+        <v>315</v>
       </c>
       <c r="D104" t="s">
-        <v>362</v>
+        <v>316</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>107</v>
+        <v>317</v>
       </c>
       <c r="B105" t="s">
-        <v>249</v>
+        <v>318</v>
       </c>
       <c r="C105" t="s">
-        <v>363</v>
+        <v>319</v>
       </c>
       <c r="D105" t="s">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>108</v>
+        <v>320</v>
       </c>
       <c r="B106" t="s">
-        <v>250</v>
+        <v>321</v>
       </c>
       <c r="C106" t="s">
-        <v>364</v>
+        <v>322</v>
       </c>
       <c r="D106" t="s">
-        <v>364</v>
+        <v>322</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>109</v>
+        <v>323</v>
       </c>
       <c r="B107" t="s">
-        <v>251</v>
+        <v>324</v>
       </c>
       <c r="C107" t="s">
-        <v>365</v>
+        <v>325</v>
       </c>
       <c r="D107" t="s">
-        <v>365</v>
+        <v>325</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>110</v>
+        <v>326</v>
       </c>
       <c r="B108" t="s">
-        <v>252</v>
+        <v>327</v>
       </c>
       <c r="C108" t="s">
-        <v>366</v>
+        <v>328</v>
       </c>
       <c r="D108" t="s">
-        <v>366</v>
+        <v>328</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>111</v>
+        <v>329</v>
       </c>
       <c r="B109" t="s">
-        <v>253</v>
+        <v>330</v>
       </c>
       <c r="C109" t="s">
-        <v>367</v>
+        <v>331</v>
       </c>
       <c r="D109" t="s">
-        <v>367</v>
+        <v>331</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>112</v>
+        <v>332</v>
       </c>
       <c r="B110" t="s">
-        <v>254</v>
+        <v>333</v>
       </c>
       <c r="C110" t="s">
-        <v>368</v>
+        <v>334</v>
       </c>
       <c r="D110" t="s">
-        <v>368</v>
+        <v>334</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>113</v>
+        <v>335</v>
       </c>
       <c r="B111" t="s">
-        <v>255</v>
+        <v>336</v>
       </c>
       <c r="C111" t="s">
-        <v>369</v>
+        <v>337</v>
       </c>
       <c r="D111" t="s">
-        <v>369</v>
+        <v>337</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>114</v>
+        <v>338</v>
       </c>
       <c r="B112" t="s">
-        <v>256</v>
+        <v>339</v>
       </c>
       <c r="C112" t="s">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="D112" t="s">
-        <v>370</v>
+        <v>340</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>115</v>
+        <v>341</v>
       </c>
       <c r="B113" t="s">
-        <v>257</v>
+        <v>342</v>
       </c>
       <c r="C113" t="s">
-        <v>371</v>
+        <v>343</v>
       </c>
       <c r="D113" t="s">
-        <v>427</v>
+        <v>343</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>116</v>
+        <v>344</v>
       </c>
       <c r="B114" t="s">
-        <v>258</v>
+        <v>345</v>
       </c>
       <c r="C114" t="s">
-        <v>372</v>
+        <v>346</v>
       </c>
       <c r="D114" t="s">
-        <v>372</v>
+        <v>346</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>117</v>
+        <v>347</v>
       </c>
       <c r="B115" t="s">
-        <v>259</v>
+        <v>348</v>
       </c>
       <c r="C115" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="D115" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>118</v>
+        <v>350</v>
       </c>
       <c r="B116" t="s">
-        <v>260</v>
+        <v>351</v>
       </c>
       <c r="C116" t="s">
-        <v>374</v>
+        <v>352</v>
       </c>
       <c r="D116" t="s">
-        <v>374</v>
+        <v>352</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>119</v>
+        <v>353</v>
       </c>
       <c r="B117" t="s">
-        <v>119</v>
+        <v>354</v>
       </c>
       <c r="C117" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="D117" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>120</v>
+        <v>356</v>
       </c>
       <c r="B118" t="s">
-        <v>261</v>
+        <v>357</v>
       </c>
       <c r="C118" t="s">
-        <v>376</v>
+        <v>358</v>
       </c>
       <c r="D118" t="s">
-        <v>377</v>
+        <v>358</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>121</v>
+        <v>359</v>
       </c>
       <c r="B119" t="s">
-        <v>262</v>
+        <v>360</v>
       </c>
       <c r="C119" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="D119" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>122</v>
+        <v>363</v>
       </c>
       <c r="B120" t="s">
-        <v>263</v>
+        <v>364</v>
       </c>
       <c r="C120" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="D120" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>123</v>
+        <v>366</v>
       </c>
       <c r="B121" t="s">
-        <v>264</v>
+        <v>367</v>
       </c>
       <c r="C121" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="D121" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>124</v>
+        <v>369</v>
       </c>
       <c r="B122" t="s">
-        <v>265</v>
+        <v>370</v>
       </c>
       <c r="C122" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="D122" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>125</v>
+        <v>372</v>
       </c>
       <c r="B123" t="s">
-        <v>266</v>
+        <v>372</v>
       </c>
       <c r="C123" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="D123" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>126</v>
+        <v>374</v>
       </c>
       <c r="B124" t="s">
-        <v>267</v>
+        <v>375</v>
       </c>
       <c r="C124" t="s">
-        <v>295</v>
+        <v>376</v>
       </c>
       <c r="D124" t="s">
-        <v>295</v>
+        <v>377</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>127</v>
+        <v>378</v>
       </c>
       <c r="B125" t="s">
-        <v>268</v>
+        <v>379</v>
       </c>
       <c r="C125" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D125" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>128</v>
+        <v>380</v>
       </c>
       <c r="B126" t="s">
-        <v>269</v>
+        <v>381</v>
       </c>
       <c r="C126" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D126" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>129</v>
+        <v>383</v>
       </c>
       <c r="B127" t="s">
-        <v>270</v>
+        <v>384</v>
       </c>
       <c r="C127" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D127" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>130</v>
+        <v>386</v>
       </c>
       <c r="B128" t="s">
-        <v>271</v>
+        <v>387</v>
       </c>
       <c r="C128" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D128" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>131</v>
+        <v>389</v>
       </c>
       <c r="B129" t="s">
-        <v>272</v>
+        <v>390</v>
       </c>
       <c r="C129" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="D129" t="s">
-        <v>428</v>
+        <v>391</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>132</v>
+        <v>392</v>
       </c>
       <c r="B130" t="s">
-        <v>132</v>
+        <v>393</v>
       </c>
       <c r="C130" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="D130" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>133</v>
+        <v>395</v>
       </c>
       <c r="B131" t="s">
-        <v>133</v>
+        <v>396</v>
       </c>
       <c r="C131" t="s">
-        <v>388</v>
+        <v>63</v>
       </c>
       <c r="D131" t="s">
-        <v>388</v>
+        <v>63</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>134</v>
+        <v>397</v>
       </c>
       <c r="B132" t="s">
-        <v>134</v>
+        <v>398</v>
       </c>
       <c r="C132" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="D132" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>135</v>
+        <v>400</v>
       </c>
       <c r="B133" t="s">
-        <v>135</v>
+        <v>401</v>
       </c>
       <c r="C133" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="D133" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>136</v>
+        <v>403</v>
       </c>
       <c r="B134" t="s">
-        <v>136</v>
+        <v>404</v>
       </c>
       <c r="C134" t="s">
-        <v>391</v>
+        <v>205</v>
       </c>
       <c r="D134" t="s">
-        <v>391</v>
+        <v>205</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>137</v>
+        <v>405</v>
       </c>
       <c r="B135" t="s">
-        <v>137</v>
+        <v>406</v>
       </c>
       <c r="C135" t="s">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="D135" t="s">
-        <v>392</v>
+        <v>407</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>138</v>
+        <v>408</v>
       </c>
       <c r="B136" t="s">
-        <v>138</v>
+        <v>409</v>
       </c>
       <c r="C136" t="s">
-        <v>393</v>
+        <v>410</v>
       </c>
       <c r="D136" t="s">
-        <v>393</v>
+        <v>410</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>139</v>
+        <v>411</v>
       </c>
       <c r="B137" t="s">
-        <v>139</v>
+        <v>412</v>
       </c>
       <c r="C137" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="D137" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>140</v>
+        <v>415</v>
       </c>
       <c r="B138" t="s">
-        <v>140</v>
+        <v>415</v>
       </c>
       <c r="C138" t="s">
-        <v>395</v>
+        <v>416</v>
       </c>
       <c r="D138" t="s">
-        <v>395</v>
+        <v>416</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>141</v>
+        <v>417</v>
       </c>
       <c r="B139" t="s">
-        <v>141</v>
+        <v>417</v>
       </c>
       <c r="C139" t="s">
-        <v>141</v>
+        <v>418</v>
       </c>
       <c r="D139" t="s">
-        <v>141</v>
+        <v>418</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>142</v>
+        <v>419</v>
       </c>
       <c r="B140" t="s">
-        <v>142</v>
+        <v>419</v>
       </c>
       <c r="C140" t="s">
-        <v>347</v>
+        <v>420</v>
       </c>
       <c r="D140" t="s">
-        <v>347</v>
+        <v>420</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="B141" t="s">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="C141" t="s">
-        <v>396</v>
+        <v>421</v>
       </c>
       <c r="D141" t="s">
-        <v>396</v>
+        <v>421</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>144</v>
+        <v>422</v>
       </c>
       <c r="B142" t="s">
-        <v>144</v>
+        <v>422</v>
       </c>
       <c r="C142" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="D142" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>145</v>
+        <v>424</v>
       </c>
       <c r="B143" t="s">
-        <v>145</v>
+        <v>424</v>
       </c>
       <c r="C143" t="s">
-        <v>398</v>
+        <v>425</v>
       </c>
       <c r="D143" t="s">
-        <v>398</v>
+        <v>425</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>146</v>
+        <v>426</v>
       </c>
       <c r="B144" t="s">
-        <v>146</v>
+        <v>426</v>
       </c>
       <c r="C144" t="s">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="D144" t="s">
-        <v>399</v>
+        <v>427</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>147</v>
+        <v>428</v>
       </c>
       <c r="B145" t="s">
-        <v>147</v>
+        <v>428</v>
       </c>
       <c r="C145" t="s">
-        <v>400</v>
+        <v>429</v>
       </c>
       <c r="D145" t="s">
-        <v>400</v>
+        <v>429</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>148</v>
+        <v>430</v>
       </c>
       <c r="B146" t="s">
-        <v>148</v>
+        <v>430</v>
       </c>
       <c r="C146" t="s">
-        <v>401</v>
+        <v>431</v>
       </c>
       <c r="D146" t="s">
-        <v>401</v>
+        <v>431</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>149</v>
+        <v>432</v>
       </c>
       <c r="B147" t="s">
-        <v>149</v>
+        <v>432</v>
       </c>
       <c r="C147" t="s">
-        <v>149</v>
+        <v>432</v>
       </c>
       <c r="D147" t="s">
-        <v>149</v>
+        <v>432</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>150</v>
+        <v>272</v>
       </c>
       <c r="B148" t="s">
-        <v>150</v>
+        <v>272</v>
       </c>
       <c r="C148" t="s">
-        <v>402</v>
+        <v>273</v>
       </c>
       <c r="D148" t="s">
-        <v>402</v>
+        <v>273</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>151</v>
+        <v>284</v>
       </c>
       <c r="B149" t="s">
-        <v>151</v>
+        <v>284</v>
       </c>
       <c r="C149" t="s">
-        <v>403</v>
+        <v>286</v>
       </c>
       <c r="D149" t="s">
-        <v>403</v>
+        <v>286</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>152</v>
+        <v>433</v>
       </c>
       <c r="B150" t="s">
-        <v>152</v>
+        <v>433</v>
       </c>
       <c r="C150" t="s">
-        <v>152</v>
+        <v>434</v>
       </c>
       <c r="D150" t="s">
-        <v>152</v>
+        <v>434</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>435</v>
+      </c>
+      <c r="B151" t="s">
+        <v>435</v>
+      </c>
+      <c r="C151" t="s">
+        <v>436</v>
+      </c>
+      <c r="D151" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>301</v>
+      </c>
+      <c r="B152" t="s">
+        <v>301</v>
+      </c>
+      <c r="C152" t="s">
+        <v>437</v>
+      </c>
+      <c r="D152" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>438</v>
+      </c>
+      <c r="B153" t="s">
+        <v>438</v>
+      </c>
+      <c r="C153" t="s">
+        <v>439</v>
+      </c>
+      <c r="D153" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>440</v>
+      </c>
+      <c r="B154" t="s">
+        <v>440</v>
+      </c>
+      <c r="C154" t="s">
+        <v>441</v>
+      </c>
+      <c r="D154" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>442</v>
+      </c>
+      <c r="B155" t="s">
+        <v>442</v>
+      </c>
+      <c r="C155" t="s">
+        <v>442</v>
+      </c>
+      <c r="D155" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>443</v>
+      </c>
+      <c r="B156" t="s">
+        <v>443</v>
+      </c>
+      <c r="C156" t="s">
+        <v>444</v>
+      </c>
+      <c r="D156" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>445</v>
+      </c>
+      <c r="B157" t="s">
+        <v>445</v>
+      </c>
+      <c r="C157" t="s">
+        <v>446</v>
+      </c>
+      <c r="D157" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>447</v>
+      </c>
+      <c r="B158" t="s">
+        <v>447</v>
+      </c>
+      <c r="C158" t="s">
+        <v>447</v>
+      </c>
+      <c r="D158" t="s">
+        <v>447</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>